--- a/SAM CN COMM  1.xlsx
+++ b/SAM CN COMM  1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aumovio-my.sharepoint.com/personal/uidv9144_automotive-wan_com/Documents/Y 2026/VIO/SAM China Communication Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B21D0288-16A8-46DB-BFA8-1006C3681FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D29D89-D9D6-44D9-896A-B470D6761CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="92">
   <si>
     <t>Year</t>
   </si>
@@ -311,13 +311,19 @@
   </si>
   <si>
     <t>Road show - TBD</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,13 +678,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -702,6 +701,13 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -920,13 +926,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -950,6 +949,13 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -990,14 +996,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:J90" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" headerRowBorderDxfId="23" tableBorderDxfId="24">
-  <autoFilter ref="A2:J90" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2026"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87AE0588-74B1-435D-89DA-BDDFAE4D4F08}" name="Table13" displayName="Table13" ref="A2:J90" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23">
+  <autoFilter ref="A2:J90" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{887A09BA-E193-41CE-830F-B59E6BD137A0}" name="Year" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{63EC88A9-C4E0-409C-8163-247BDCC14BC5}" name="Month" dataDxfId="21"/>
@@ -1015,7 +1015,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}" name="Table1" displayName="Table1" ref="A2:I75" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}" name="Table1" displayName="Table1" ref="A2:I75" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
   <autoFilter ref="A2:I75" xr:uid="{4AF62893-D76B-41CA-862A-2A0CA5F92DCA}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{C1456486-B736-420F-9D6E-5A25F22F3117}" name="Month" dataDxfId="8"/>
@@ -1296,20 +1296,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C514591A-F47A-421D-8C5F-2D1DE3B987E2}">
   <dimension ref="A2:J90"/>
-  <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" style="2" customWidth="1"/>
-    <col min="8" max="10" width="17.5703125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.85546875" style="1"/>
+    <col min="2" max="2" width="16.1796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.81640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" style="2" customWidth="1"/>
+    <col min="8" max="10" width="17.54296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>2026</v>
       </c>
@@ -1364,7 +1364,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2026</v>
       </c>
@@ -1390,7 +1390,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>2026</v>
       </c>
@@ -1416,7 +1416,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>2026</v>
       </c>
@@ -1439,7 +1439,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>2026</v>
       </c>
@@ -1465,7 +1465,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>2026</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>2026</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>2026</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>2026</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>2026</v>
       </c>
@@ -1591,7 +1591,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>2026</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>2026</v>
       </c>
@@ -1639,7 +1639,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>2026</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>2026</v>
       </c>
@@ -1685,7 +1685,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>2026</v>
       </c>
@@ -1713,7 +1713,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>2026</v>
       </c>
@@ -1736,7 +1736,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>2026</v>
       </c>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>2026</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>2026</v>
       </c>
@@ -1812,7 +1812,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" ht="30">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>2026</v>
       </c>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>2026</v>
       </c>
@@ -1856,7 +1856,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>2026</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>2026</v>
       </c>
@@ -1908,7 +1908,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>2026</v>
       </c>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>2026</v>
       </c>
@@ -1957,7 +1957,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>2026</v>
       </c>
@@ -1983,7 +1983,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>2026</v>
       </c>
@@ -2009,7 +2009,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>2026</v>
       </c>
@@ -2035,7 +2035,7 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>2026</v>
       </c>
@@ -2060,7 +2060,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>2026</v>
       </c>
@@ -2085,7 +2085,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>2026</v>
       </c>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>2026</v>
       </c>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>2026</v>
       </c>
@@ -2156,7 +2156,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>2026</v>
       </c>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>2026</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>2026</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>2026</v>
       </c>
@@ -2255,7 +2255,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>2026</v>
       </c>
@@ -2277,7 +2277,7 @@
       <c r="G40" s="1"/>
       <c r="J40" s="18"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>2026</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>2026</v>
       </c>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>2026</v>
       </c>
@@ -2351,7 +2351,7 @@
       <c r="I43" s="15"/>
       <c r="J43" s="15"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>2026</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>2026</v>
       </c>
@@ -2401,7 +2401,7 @@
       <c r="I45" s="15"/>
       <c r="J45" s="15"/>
     </row>
-    <row r="46" spans="1:10" ht="30">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>2026</v>
       </c>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>2026</v>
       </c>
@@ -2446,7 +2446,7 @@
       <c r="I47" s="15"/>
       <c r="J47" s="15"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>2026</v>
       </c>
@@ -2470,7 +2470,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>2026</v>
       </c>
@@ -2494,7 +2494,7 @@
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>2026</v>
       </c>
@@ -2518,7 +2518,7 @@
       <c r="I50" s="15"/>
       <c r="J50" s="15"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
         <v>2026</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>2026</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>2026</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="10">
         <v>2026</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>2026</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>2026</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>2026</v>
       </c>
@@ -2692,7 +2692,7 @@
       <c r="I57" s="15"/>
       <c r="J57" s="15"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="10">
         <v>2026</v>
       </c>
@@ -2716,7 +2716,7 @@
       <c r="I58" s="15"/>
       <c r="J58" s="15"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="10">
         <v>2026</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
         <v>2026</v>
       </c>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
         <v>2026</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
         <v>2027</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>2027</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="10">
         <v>2027</v>
       </c>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:8" hidden="1">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
@@ -2879,16 +2879,30 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="1:8" hidden="1">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="10">
+        <v>2027</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2897,7 +2911,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:8" hidden="1">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2906,7 +2920,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:8" hidden="1">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2915,7 +2929,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:8" hidden="1">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2924,7 +2938,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:8" hidden="1">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2933,7 +2947,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:8" hidden="1">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2942,7 +2956,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:8" hidden="1">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2951,7 +2965,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:8" hidden="1">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2960,7 +2974,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:8" hidden="1">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2969,7 +2983,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:8" hidden="1">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2978,7 +2992,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:8" hidden="1">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2987,7 +3001,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:8" hidden="1">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2996,7 +3010,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:8" hidden="1">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3005,7 +3019,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:8" hidden="1">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3014,16 +3028,16 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" s="1" customFormat="1" hidden="1"/>
-    <row r="82" s="1" customFormat="1" hidden="1"/>
-    <row r="83" s="1" customFormat="1" hidden="1"/>
-    <row r="84" s="1" customFormat="1" hidden="1"/>
-    <row r="85" s="1" customFormat="1" hidden="1"/>
-    <row r="86" s="1" customFormat="1" hidden="1"/>
-    <row r="87" s="1" customFormat="1" hidden="1"/>
-    <row r="88" s="1" customFormat="1" hidden="1"/>
-    <row r="89" s="1" customFormat="1" hidden="1"/>
-    <row r="90" s="1" customFormat="1" hidden="1"/>
+    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="90" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3043,19 +3057,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A00FF8-6E21-4DE8-B251-028D36ABCD64}">
   <dimension ref="A2:I75"/>
-  <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.81640625" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="9" width="17.5703125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.85546875" style="1"/>
+    <col min="2" max="2" width="13.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.54296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="2" customWidth="1"/>
+    <col min="7" max="9" width="17.54296875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -3084,7 +3098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -3107,7 +3121,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
@@ -3130,7 +3144,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
@@ -3151,7 +3165,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -3174,7 +3188,7 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>14</v>
       </c>
@@ -3197,7 +3211,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
@@ -3222,7 +3236,7 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
@@ -3243,7 +3257,7 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>24</v>
       </c>
@@ -3266,7 +3280,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>26</v>
       </c>
@@ -3289,7 +3303,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>26</v>
       </c>
@@ -3312,7 +3326,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
@@ -3337,7 +3351,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>26</v>
       </c>
@@ -3362,7 +3376,7 @@
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
@@ -3385,7 +3399,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>26</v>
       </c>
@@ -3408,7 +3422,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>32</v>
       </c>
@@ -3431,7 +3445,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>32</v>
       </c>
@@ -3454,7 +3468,7 @@
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -3477,7 +3491,7 @@
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>35</v>
       </c>
@@ -3502,7 +3516,7 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>38</v>
       </c>
@@ -3525,7 +3539,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>38</v>
       </c>
@@ -3548,7 +3562,7 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>38</v>
       </c>
@@ -3571,7 +3585,7 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
         <v>43</v>
       </c>
@@ -3594,7 +3608,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>43</v>
       </c>
@@ -3617,7 +3631,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
         <v>43</v>
       </c>
@@ -3640,7 +3654,7 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>43</v>
       </c>
@@ -3663,7 +3677,7 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
         <v>43</v>
       </c>
@@ -3688,7 +3702,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>52</v>
       </c>
@@ -3711,7 +3725,7 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>52</v>
       </c>
@@ -3736,7 +3750,7 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>52</v>
       </c>
@@ -3761,7 +3775,7 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>52</v>
       </c>
@@ -3786,7 +3800,7 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>60</v>
       </c>
@@ -3811,7 +3825,7 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
         <v>60</v>
       </c>
@@ -3836,7 +3850,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
@@ -3861,7 +3875,7 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>60</v>
       </c>
@@ -3886,7 +3900,7 @@
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>60</v>
       </c>
@@ -3911,7 +3925,7 @@
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
         <v>60</v>
       </c>
@@ -3936,7 +3950,7 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>60</v>
       </c>
@@ -3961,7 +3975,7 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>68</v>
       </c>
@@ -3986,7 +4000,7 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>70</v>
       </c>
@@ -4011,7 +4025,7 @@
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -4019,7 +4033,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -4027,7 +4041,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -4035,7 +4049,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -4043,7 +4057,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -4051,7 +4065,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -4059,7 +4073,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -4067,33 +4081,33 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
     </row>
-    <row r="49" s="1" customFormat="1"/>
-    <row r="50" s="1" customFormat="1"/>
-    <row r="51" s="1" customFormat="1"/>
-    <row r="52" s="1" customFormat="1"/>
-    <row r="53" s="1" customFormat="1"/>
-    <row r="54" s="1" customFormat="1"/>
-    <row r="55" s="1" customFormat="1"/>
-    <row r="56" s="1" customFormat="1"/>
-    <row r="57" s="1" customFormat="1"/>
-    <row r="58" s="1" customFormat="1"/>
-    <row r="59" s="1" customFormat="1"/>
-    <row r="60" s="1" customFormat="1"/>
-    <row r="61" s="1" customFormat="1"/>
-    <row r="62" s="1" customFormat="1"/>
-    <row r="63" s="1" customFormat="1"/>
-    <row r="64" s="1" customFormat="1"/>
-    <row r="65" s="1" customFormat="1"/>
-    <row r="66" s="1" customFormat="1"/>
-    <row r="67" s="1" customFormat="1"/>
-    <row r="68" s="1" customFormat="1"/>
-    <row r="69" s="1" customFormat="1"/>
-    <row r="70" s="1" customFormat="1"/>
-    <row r="71" s="1" customFormat="1"/>
-    <row r="72" s="1" customFormat="1"/>
-    <row r="73" s="1" customFormat="1"/>
-    <row r="74" s="1" customFormat="1"/>
-    <row r="75" s="1" customFormat="1"/>
+    <row r="49" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="50" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="51" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="52" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="53" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="54" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="55" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="56" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="57" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="58" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="59" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="60" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="61" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="62" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="63" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="64" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="65" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="66" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="67" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="68" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="69" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="70" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="71" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="72" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="73" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="74" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="75" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/SAM CN COMM  1.xlsx
+++ b/SAM CN COMM  1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D29D89-D9D6-44D9-896A-B470D6761CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481E5E03-3738-422A-BA85-2B68FD9326BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="91">
   <si>
     <t>Year</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>Road show - TBD</t>
-  </si>
-  <si>
-    <t>June</t>
   </si>
   <si>
     <t>test</t>
@@ -2887,16 +2884,16 @@
         <v>32</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>16</v>

--- a/SAM CN COMM  1.xlsx
+++ b/SAM CN COMM  1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uik07697\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481E5E03-3738-422A-BA85-2B68FD9326BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DE7AFD-8855-40B8-80E8-8815DD180A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2850,15 +2850,15 @@
       </c>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>2027</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D65" s="14" t="s">
         <v>15</v>
@@ -2867,24 +2867,22 @@
         <v>17</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H65" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J65" s="18"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="10">
         <v>2027</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>15</v>
@@ -2893,13 +2891,16 @@
         <v>17</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H66" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2908,7 +2909,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2917,7 +2918,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2926,7 +2927,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2935,7 +2936,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2944,7 +2945,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2953,7 +2954,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2962,7 +2963,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2971,7 +2972,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2980,7 +2981,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2989,7 +2990,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2998,7 +2999,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3007,7 +3008,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3016,7 +3017,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3025,16 +3026,96 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="90" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
